--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/39.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/39.xlsx
@@ -426,13 +426,13 @@
         <v>-6.155074837743746</v>
       </c>
       <c r="E2">
-        <v>-4.677376838224168</v>
+        <v>-4.610074657522172</v>
       </c>
       <c r="F2">
-        <v>-2.098137978734861</v>
+        <v>-2.040815782828538</v>
       </c>
       <c r="G2">
-        <v>-6.907732504182964</v>
+        <v>-6.440743639867832</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-5.606748758015526</v>
       </c>
       <c r="E3">
-        <v>-5.28696378134469</v>
+        <v>-5.638948480538884</v>
       </c>
       <c r="F3">
-        <v>-2.045670015808943</v>
+        <v>-2.118713796652998</v>
       </c>
       <c r="G3">
-        <v>-6.10180005592063</v>
+        <v>-5.991323840729611</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-5.09474956320996</v>
       </c>
       <c r="E4">
-        <v>-5.984394063266002</v>
+        <v>-6.235108498226664</v>
       </c>
       <c r="F4">
-        <v>-2.195786756544269</v>
+        <v>-2.249392067914231</v>
       </c>
       <c r="G4">
-        <v>-6.506315615364176</v>
+        <v>-5.890219779960269</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-4.693306229198375</v>
       </c>
       <c r="E5">
-        <v>-6.466595032550758</v>
+        <v>-6.40112235534786</v>
       </c>
       <c r="F5">
-        <v>-1.956072140787343</v>
+        <v>-2.071576377964095</v>
       </c>
       <c r="G5">
-        <v>-5.976922967633781</v>
+        <v>-6.007525650598804</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-4.386798902617712</v>
       </c>
       <c r="E6">
-        <v>-6.792432322824663</v>
+        <v>-7.999641980737442</v>
       </c>
       <c r="F6">
-        <v>-2.414426877206574</v>
+        <v>-2.460861840337903</v>
       </c>
       <c r="G6">
-        <v>-5.88149318191875</v>
+        <v>-5.546651363894705</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-4.181495381343868</v>
       </c>
       <c r="E7">
-        <v>-7.223130957220183</v>
+        <v>-8.613698527703535</v>
       </c>
       <c r="F7">
-        <v>-2.288312081967363</v>
+        <v>-2.240196361375753</v>
       </c>
       <c r="G7">
-        <v>-5.303915543864263</v>
+        <v>-5.617387790432312</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-4.062193741826346</v>
       </c>
       <c r="E8">
-        <v>-9.181333687616998</v>
+        <v>-9.391975656083785</v>
       </c>
       <c r="F8">
-        <v>-2.272025550460922</v>
+        <v>-2.030041208020325</v>
       </c>
       <c r="G8">
-        <v>-4.772861002273154</v>
+        <v>-4.971897621185216</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-4.01560965113801</v>
       </c>
       <c r="E9">
-        <v>-9.594439200492719</v>
+        <v>-10.245801316334</v>
       </c>
       <c r="F9">
-        <v>-2.037634023634385</v>
+        <v>-2.172540282119507</v>
       </c>
       <c r="G9">
-        <v>-4.831404689589625</v>
+        <v>-4.474892040465511</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-4.019447334631014</v>
       </c>
       <c r="E10">
-        <v>-10.82375234003694</v>
+        <v>-11.64236911487752</v>
       </c>
       <c r="F10">
-        <v>-2.332986764367743</v>
+        <v>-1.921849798275487</v>
       </c>
       <c r="G10">
-        <v>-4.739460908327447</v>
+        <v>-4.023217759815047</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-4.049924481432472</v>
       </c>
       <c r="E11">
-        <v>-10.65499422766709</v>
+        <v>-11.94099027636532</v>
       </c>
       <c r="F11">
-        <v>-2.116512824463759</v>
+        <v>-2.129356661044166</v>
       </c>
       <c r="G11">
-        <v>-4.261818708466939</v>
+        <v>-4.30706062380662</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-4.085662095917783</v>
       </c>
       <c r="E12">
-        <v>-12.15554484637474</v>
+        <v>-12.66732580787759</v>
       </c>
       <c r="F12">
-        <v>-2.128727101818038</v>
+        <v>-2.303114179087987</v>
       </c>
       <c r="G12">
-        <v>-4.191880123404296</v>
+        <v>-3.306474718926217</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-4.102423607653743</v>
       </c>
       <c r="E13">
-        <v>-12.43475696826567</v>
+        <v>-13.54046088129652</v>
       </c>
       <c r="F13">
-        <v>-2.03244264512104</v>
+        <v>-1.890054572253833</v>
       </c>
       <c r="G13">
-        <v>-2.862345171559752</v>
+        <v>-3.115337061670856</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.085975876524643</v>
       </c>
       <c r="E14">
-        <v>-14.50796029608727</v>
+        <v>-15.05517656670015</v>
       </c>
       <c r="F14">
-        <v>-1.807415811783152</v>
+        <v>-1.75719852309064</v>
       </c>
       <c r="G14">
-        <v>-2.928754715077532</v>
+        <v>-2.784444724475162</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-4.021916832064806</v>
       </c>
       <c r="E15">
-        <v>-14.14700016140988</v>
+        <v>-15.43378869305945</v>
       </c>
       <c r="F15">
-        <v>-1.611746319200478</v>
+        <v>-1.82136386211149</v>
       </c>
       <c r="G15">
-        <v>-2.451691860686397</v>
+        <v>-1.982024765029994</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-3.907944498246632</v>
       </c>
       <c r="E16">
-        <v>-15.31584911600368</v>
+        <v>-15.39511552503394</v>
       </c>
       <c r="F16">
-        <v>-1.501555230545282</v>
+        <v>-1.294284452486401</v>
       </c>
       <c r="G16">
-        <v>-2.746181439132265</v>
+        <v>-1.484525913024938</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-3.747324325319922</v>
       </c>
       <c r="E17">
-        <v>-17.24918599562438</v>
+        <v>-17.3704675864978</v>
       </c>
       <c r="F17">
-        <v>-1.052104615338743</v>
+        <v>-1.19656112161074</v>
       </c>
       <c r="G17">
-        <v>-1.210227351823084</v>
+        <v>-1.137517840144071</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-3.554149303575456</v>
       </c>
       <c r="E18">
-        <v>-16.76216672999546</v>
+        <v>-17.59939553300756</v>
       </c>
       <c r="F18">
-        <v>-0.7807099166291522</v>
+        <v>-0.9921275019064476</v>
       </c>
       <c r="G18">
-        <v>-2.063073540922431</v>
+        <v>-0.8795071629954316</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-3.346335815891281</v>
       </c>
       <c r="E19">
-        <v>-17.75559618695414</v>
+        <v>-18.0208334380574</v>
       </c>
       <c r="F19">
-        <v>-0.6494915498212938</v>
+        <v>-0.4296320723420685</v>
       </c>
       <c r="G19">
-        <v>-2.334124456950259</v>
+        <v>-0.7360380509600362</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.147380354525105</v>
       </c>
       <c r="E20">
-        <v>-18.64943997201014</v>
+        <v>-18.57205287969306</v>
       </c>
       <c r="F20">
-        <v>-0.6416344850057404</v>
+        <v>-0.4926310700597765</v>
       </c>
       <c r="G20">
-        <v>-1.763022245970587</v>
+        <v>-0.8589619173787146</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-2.978336721059064</v>
       </c>
       <c r="E21">
-        <v>-19.96688627269164</v>
+        <v>-20.39250848772456</v>
       </c>
       <c r="F21">
-        <v>-0.06361296521069018</v>
+        <v>0.04191441496674443</v>
       </c>
       <c r="G21">
-        <v>-1.430663337100995</v>
+        <v>-0.8838505987429555</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-2.859810804708068</v>
       </c>
       <c r="E22">
-        <v>-19.98754969958863</v>
+        <v>-20.02830143718366</v>
       </c>
       <c r="F22">
-        <v>0.3402368528391388</v>
+        <v>0.3968706754337354</v>
       </c>
       <c r="G22">
-        <v>-1.885999081117893</v>
+        <v>-1.003483782895598</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-2.804800645641472</v>
       </c>
       <c r="E23">
-        <v>-20.52459048910628</v>
+        <v>-20.65428598468596</v>
       </c>
       <c r="F23">
-        <v>0.6991063209169546</v>
+        <v>0.4059959707429747</v>
       </c>
       <c r="G23">
-        <v>-2.524255708361682</v>
+        <v>-1.186689373038866</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-2.819924593790781</v>
       </c>
       <c r="E24">
-        <v>-21.80098617290825</v>
+        <v>-21.54042683545491</v>
       </c>
       <c r="F24">
-        <v>0.8002582644728022</v>
+        <v>0.4952161102288983</v>
       </c>
       <c r="G24">
-        <v>-2.656939063030132</v>
+        <v>-1.436880541623746</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-2.902546955609803</v>
       </c>
       <c r="E25">
-        <v>-20.82664876236591</v>
+        <v>-21.48739387635108</v>
       </c>
       <c r="F25">
-        <v>0.9824841824754431</v>
+        <v>0.813063167785277</v>
       </c>
       <c r="G25">
-        <v>-3.100860046027623</v>
+        <v>-1.567415352237209</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-3.040448645782869</v>
       </c>
       <c r="E26">
-        <v>-21.25306346035017</v>
+        <v>-21.85665923235855</v>
       </c>
       <c r="F26">
-        <v>0.9325518521694944</v>
+        <v>0.7220587249137234</v>
       </c>
       <c r="G26">
-        <v>-2.993088546542189</v>
+        <v>-1.413057855923151</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-3.216609299445377</v>
       </c>
       <c r="E27">
-        <v>-21.64685956005718</v>
+        <v>-20.82526757779357</v>
       </c>
       <c r="F27">
-        <v>0.9402457286066963</v>
+        <v>0.9836356131653344</v>
       </c>
       <c r="G27">
-        <v>-3.6359666953588</v>
+        <v>-2.431222757617083</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-3.405493478722343</v>
       </c>
       <c r="E28">
-        <v>-21.50583382251031</v>
+        <v>-21.44774708641393</v>
       </c>
       <c r="F28">
-        <v>1.212725588613955</v>
+        <v>1.10679893534837</v>
       </c>
       <c r="G28">
-        <v>-3.496678802339504</v>
+        <v>-2.82733284193642</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-3.58208369686628</v>
       </c>
       <c r="E29">
-        <v>-21.60627990447445</v>
+        <v>-21.81977934004007</v>
       </c>
       <c r="F29">
-        <v>1.145732203279947</v>
+        <v>0.9997374187409512</v>
       </c>
       <c r="G29">
-        <v>-3.917515351291657</v>
+        <v>-3.048662674509934</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-3.718357997347604</v>
       </c>
       <c r="E30">
-        <v>-21.02089765492493</v>
+        <v>-20.92177841584504</v>
       </c>
       <c r="F30">
-        <v>0.9215113714249826</v>
+        <v>1.14955594721127</v>
       </c>
       <c r="G30">
-        <v>-4.095040045289536</v>
+        <v>-3.159420286071791</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-3.791638253538065</v>
       </c>
       <c r="E31">
-        <v>-20.43663393845529</v>
+        <v>-19.97552660109827</v>
       </c>
       <c r="F31">
-        <v>0.9083105084939698</v>
+        <v>1.507964014645726</v>
       </c>
       <c r="G31">
-        <v>-4.494106446775442</v>
+        <v>-3.267046121553498</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-3.782973100513939</v>
       </c>
       <c r="E32">
-        <v>-20.2065014178595</v>
+        <v>-20.03036642133116</v>
       </c>
       <c r="F32">
-        <v>1.167070947576063</v>
+        <v>0.9557925280224374</v>
       </c>
       <c r="G32">
-        <v>-4.492133361634036</v>
+        <v>-3.343354196233698</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-3.683254372633227</v>
       </c>
       <c r="E33">
-        <v>-19.77598845089829</v>
+        <v>-20.89203992703667</v>
       </c>
       <c r="F33">
-        <v>0.6644275479661561</v>
+        <v>0.8165638484295077</v>
       </c>
       <c r="G33">
-        <v>-4.342129232704119</v>
+        <v>-3.759900278166956</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-3.493055571934202</v>
       </c>
       <c r="E34">
-        <v>-19.07546974970375</v>
+        <v>-19.9514577617475</v>
       </c>
       <c r="F34">
-        <v>1.008251378906925</v>
+        <v>1.024899906968389</v>
       </c>
       <c r="G34">
-        <v>-3.92840704611586</v>
+        <v>-3.62465787179665</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-3.223353775057338</v>
       </c>
       <c r="E35">
-        <v>-18.54742703803934</v>
+        <v>-19.59739449298379</v>
       </c>
       <c r="F35">
-        <v>1.110869532765727</v>
+        <v>0.9551994169620329</v>
       </c>
       <c r="G35">
-        <v>-4.592893125667294</v>
+        <v>-3.636635425557733</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-2.893489239263454</v>
       </c>
       <c r="E36">
-        <v>-18.65478357133919</v>
+        <v>-19.22747250824521</v>
       </c>
       <c r="F36">
-        <v>0.8806231564227991</v>
+        <v>0.7667160115986447</v>
       </c>
       <c r="G36">
-        <v>-4.473375810608525</v>
+        <v>-3.872866023603507</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-2.528828150092576</v>
       </c>
       <c r="E37">
-        <v>-18.05756389073361</v>
+        <v>-18.06590986832975</v>
       </c>
       <c r="F37">
-        <v>0.911945384657454</v>
+        <v>1.003145322236068</v>
       </c>
       <c r="G37">
-        <v>-3.866364112164379</v>
+        <v>-3.606416765875265</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.15948490132882</v>
       </c>
       <c r="E38">
-        <v>-18.06356864726778</v>
+        <v>-18.22164408945353</v>
       </c>
       <c r="F38">
-        <v>0.6917305375624279</v>
+        <v>0.9329080501526983</v>
       </c>
       <c r="G38">
-        <v>-3.924831656933447</v>
+        <v>-3.016530519505768</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-1.815011651678429</v>
       </c>
       <c r="E39">
-        <v>-18.0455136213992</v>
+        <v>-17.40875583423266</v>
       </c>
       <c r="F39">
-        <v>0.3214171738149368</v>
+        <v>0.6018162261929583</v>
       </c>
       <c r="G39">
-        <v>-3.658627379575111</v>
+        <v>-3.238131816813503</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-1.523498368777058</v>
       </c>
       <c r="E40">
-        <v>-16.86136295313348</v>
+        <v>-17.07887914514391</v>
       </c>
       <c r="F40">
-        <v>0.4885237299816811</v>
+        <v>0.4524764940814578</v>
       </c>
       <c r="G40">
-        <v>-3.172993522782803</v>
+        <v>-3.053582145181291</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-1.303280404078574</v>
       </c>
       <c r="E41">
-        <v>-16.30193791659592</v>
+        <v>-16.84371548992559</v>
       </c>
       <c r="F41">
-        <v>0.6038134200011078</v>
+        <v>0.4755349291057848</v>
       </c>
       <c r="G41">
-        <v>-3.213779443826624</v>
+        <v>-2.463119863887961</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-1.167270578209789</v>
       </c>
       <c r="E42">
-        <v>-15.85231026084834</v>
+        <v>-16.76364754099597</v>
       </c>
       <c r="F42">
-        <v>0.3507695443657345</v>
+        <v>0.2415410186325917</v>
       </c>
       <c r="G42">
-        <v>-2.356944047352456</v>
+        <v>-2.579224006495741</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-1.11592026722307</v>
       </c>
       <c r="E43">
-        <v>-15.64791758651214</v>
+        <v>-16.80963872301787</v>
       </c>
       <c r="F43">
-        <v>0.4177745268433809</v>
+        <v>0.4839784780425202</v>
       </c>
       <c r="G43">
-        <v>-2.919763273392872</v>
+        <v>-2.268764356368428</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.145459339370565</v>
       </c>
       <c r="E44">
-        <v>-15.75251627914131</v>
+        <v>-15.02316478393993</v>
       </c>
       <c r="F44">
-        <v>0.2465907463200575</v>
+        <v>0.3731586585285995</v>
       </c>
       <c r="G44">
-        <v>-3.071475643821052</v>
+        <v>-2.208793823924531</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.243895490500479</v>
       </c>
       <c r="E45">
-        <v>-15.18156174778022</v>
+        <v>-14.6225714447474</v>
       </c>
       <c r="F45">
-        <v>0.1916095166940459</v>
+        <v>0.1993191321119009</v>
       </c>
       <c r="G45">
-        <v>-2.280503550850684</v>
+        <v>-2.030749374276987</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.398434659926414</v>
       </c>
       <c r="E46">
-        <v>-14.2457888218872</v>
+        <v>-13.97425699191328</v>
       </c>
       <c r="F46">
-        <v>0.1235135743469125</v>
+        <v>0.1035838830029592</v>
       </c>
       <c r="G46">
-        <v>-2.678782042498243</v>
+        <v>-1.884270976346394</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.592640541606041</v>
       </c>
       <c r="E47">
-        <v>-12.81239094423931</v>
+        <v>-13.92498719470983</v>
       </c>
       <c r="F47">
-        <v>-0.3982352910411617</v>
+        <v>-0.07497650924229381</v>
       </c>
       <c r="G47">
-        <v>-2.579839767966045</v>
+        <v>-2.522259449401501</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.812678705631447</v>
       </c>
       <c r="E48">
-        <v>-11.85001776202523</v>
+        <v>-13.01395785079472</v>
       </c>
       <c r="F48">
-        <v>-0.444970951539707</v>
+        <v>-0.2538988980425702</v>
       </c>
       <c r="G48">
-        <v>-2.328191959343885</v>
+        <v>-2.36087697545311</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.043687428971705</v>
       </c>
       <c r="E49">
-        <v>-12.66105387137697</v>
+        <v>-12.31511015650901</v>
       </c>
       <c r="F49">
-        <v>-0.3753872613371457</v>
+        <v>-0.06877866433454791</v>
       </c>
       <c r="G49">
-        <v>-2.62147318866792</v>
+        <v>-1.852261311527181</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.277056215716391</v>
       </c>
       <c r="E50">
-        <v>-11.94902378925493</v>
+        <v>-12.5523795521409</v>
       </c>
       <c r="F50">
-        <v>-0.03759063161914652</v>
+        <v>-0.1850168350301801</v>
       </c>
       <c r="G50">
-        <v>-2.01474619714015</v>
+        <v>-1.856164444717982</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.501912000535195</v>
       </c>
       <c r="E51">
-        <v>-12.57378112030115</v>
+        <v>-11.86854374919061</v>
       </c>
       <c r="F51">
-        <v>-0.3393698466634232</v>
+        <v>-0.1714349230938794</v>
       </c>
       <c r="G51">
-        <v>-2.849827998875768</v>
+        <v>-2.295934003609227</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.717354929418946</v>
       </c>
       <c r="E52">
-        <v>-11.00092888558704</v>
+        <v>-10.98948090329565</v>
       </c>
       <c r="F52">
-        <v>-0.2443080602529575</v>
+        <v>-0.5614203559230531</v>
       </c>
       <c r="G52">
-        <v>-2.543264860848177</v>
+        <v>-2.376297496575035</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-2.92236067511631</v>
       </c>
       <c r="E53">
-        <v>-11.05149382635669</v>
+        <v>-10.70979782010792</v>
       </c>
       <c r="F53">
-        <v>-0.3142703143585982</v>
+        <v>-0.3719130884498046</v>
       </c>
       <c r="G53">
-        <v>-2.930340466390843</v>
+        <v>-2.052244746463475</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.124419482613894</v>
       </c>
       <c r="E54">
-        <v>-10.48060722210572</v>
+        <v>-10.20767156518942</v>
       </c>
       <c r="F54">
-        <v>-0.5631466735904872</v>
+        <v>-0.3394145785031744</v>
       </c>
       <c r="G54">
-        <v>-3.082052836819023</v>
+        <v>-2.566233425799641</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.327529700140326</v>
       </c>
       <c r="E55">
-        <v>-9.609156741017648</v>
+        <v>-9.606385314924953</v>
       </c>
       <c r="F55">
-        <v>-0.8487329626448392</v>
+        <v>-0.375522285223802</v>
       </c>
       <c r="G55">
-        <v>-2.923262520027881</v>
+        <v>-2.420228435881163</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.537096420387621</v>
       </c>
       <c r="E56">
-        <v>-9.95150484752352</v>
+        <v>-9.017380286169294</v>
       </c>
       <c r="F56">
-        <v>-0.5888550559363699</v>
+        <v>-0.4402625112221946</v>
       </c>
       <c r="G56">
-        <v>-3.284244405630012</v>
+        <v>-2.990473215566165</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.752561623465647</v>
       </c>
       <c r="E57">
-        <v>-9.743262970280798</v>
+        <v>-9.165511199434198</v>
       </c>
       <c r="F57">
-        <v>-0.3881399775032441</v>
+        <v>-0.6593366964035658</v>
       </c>
       <c r="G57">
-        <v>-3.582127293253633</v>
+        <v>-3.15361027865037</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.971046645241973</v>
       </c>
       <c r="E58">
-        <v>-8.945898323958216</v>
+        <v>-8.755113714015064</v>
       </c>
       <c r="F58">
-        <v>-0.4573219095154476</v>
+        <v>-0.5440975367957098</v>
       </c>
       <c r="G58">
-        <v>-4.657630843687742</v>
+        <v>-3.235569454566107</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.186882242212269</v>
       </c>
       <c r="E59">
-        <v>-8.593062271650581</v>
+        <v>-8.242522155664833</v>
       </c>
       <c r="F59">
-        <v>-0.9364289061096117</v>
+        <v>-0.7544697224106722</v>
       </c>
       <c r="G59">
-        <v>-3.624551934339393</v>
+        <v>-3.095036796424045</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.392845499822986</v>
       </c>
       <c r="E60">
-        <v>-7.852774511720677</v>
+        <v>-7.827329016271577</v>
       </c>
       <c r="F60">
-        <v>-0.7465513584073118</v>
+        <v>-0.8069832455437441</v>
       </c>
       <c r="G60">
-        <v>-4.557000190930515</v>
+        <v>-3.773033212321245</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.583033967628285</v>
       </c>
       <c r="E61">
-        <v>-8.901836271863584</v>
+        <v>-8.050945062770339</v>
       </c>
       <c r="F61">
-        <v>-1.030197611004307</v>
+        <v>-0.9263294507346801</v>
       </c>
       <c r="G61">
-        <v>-4.364793227465969</v>
+        <v>-3.285873194035333</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.74976522627479</v>
       </c>
       <c r="E62">
-        <v>-7.883359825168482</v>
+        <v>-7.943588529470498</v>
       </c>
       <c r="F62">
-        <v>-1.085897035168546</v>
+        <v>-0.840941338854107</v>
       </c>
       <c r="G62">
-        <v>-5.005109014035185</v>
+        <v>-4.398064210135646</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.889602272949141</v>
       </c>
       <c r="E63">
-        <v>-6.653770448709796</v>
+        <v>-7.427817982366883</v>
       </c>
       <c r="F63">
-        <v>-0.8416686454337651</v>
+        <v>-0.8921170486316577</v>
       </c>
       <c r="G63">
-        <v>-4.811432168351202</v>
+        <v>-4.116436101109845</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.996985546302771</v>
       </c>
       <c r="E64">
-        <v>-7.28261699178494</v>
+        <v>-7.080121748057953</v>
       </c>
       <c r="F64">
-        <v>-0.8861569451685153</v>
+        <v>-0.7371808663468438</v>
       </c>
       <c r="G64">
-        <v>-5.544337292562754</v>
+        <v>-4.434629185616895</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-5.073610615641195</v>
       </c>
       <c r="E65">
-        <v>-6.636276953618165</v>
+        <v>-7.576279474234347</v>
       </c>
       <c r="F65">
-        <v>-1.305063997499031</v>
+        <v>-1.143525727013905</v>
       </c>
       <c r="G65">
-        <v>-5.677646340338127</v>
+        <v>-4.17460569678038</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.119410681308684</v>
       </c>
       <c r="E66">
-        <v>-6.896003051854091</v>
+        <v>-7.078102048650532</v>
       </c>
       <c r="F66">
-        <v>-1.160435190807251</v>
+        <v>-1.093350685058936</v>
       </c>
       <c r="G66">
-        <v>-5.423628181109849</v>
+        <v>-4.298479689768828</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.140845173387818</v>
       </c>
       <c r="E67">
-        <v>-7.368110052575749</v>
+        <v>-6.621015996212317</v>
       </c>
       <c r="F67">
-        <v>-1.0096897192132</v>
+        <v>-1.112208468983667</v>
       </c>
       <c r="G67">
-        <v>-5.568047419715015</v>
+        <v>-4.573314559348044</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.142717181561022</v>
       </c>
       <c r="E68">
-        <v>-6.693987826371917</v>
+        <v>-7.139730051420917</v>
       </c>
       <c r="F68">
-        <v>-1.309769124346932</v>
+        <v>-1.250058745218338</v>
       </c>
       <c r="G68">
-        <v>-5.517909207522752</v>
+        <v>-4.073557915285205</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.131621974730908</v>
       </c>
       <c r="E69">
-        <v>-6.266359497353597</v>
+        <v>-7.084863060343983</v>
       </c>
       <c r="F69">
-        <v>-1.138046905011789</v>
+        <v>-1.224642776565644</v>
       </c>
       <c r="G69">
-        <v>-5.490481337729891</v>
+        <v>-4.578134713653223</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.113971504342905</v>
       </c>
       <c r="E70">
-        <v>-6.458022631254237</v>
+        <v>-6.777266463372975</v>
       </c>
       <c r="F70">
-        <v>-1.775107826339166</v>
+        <v>-1.431149799879144</v>
       </c>
       <c r="G70">
-        <v>-5.537001123647729</v>
+        <v>-4.576628415432855</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.092992977840566</v>
       </c>
       <c r="E71">
-        <v>-6.541178999457088</v>
+        <v>-7.181206344857171</v>
       </c>
       <c r="F71">
-        <v>-1.299063304033151</v>
+        <v>-1.388694313750863</v>
       </c>
       <c r="G71">
-        <v>-5.634602627236522</v>
+        <v>-4.508460972233721</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.072963832287087</v>
       </c>
       <c r="E72">
-        <v>-6.99379997652374</v>
+        <v>-7.119034925205864</v>
       </c>
       <c r="F72">
-        <v>-1.446346199883501</v>
+        <v>-1.195948129732669</v>
       </c>
       <c r="G72">
-        <v>-5.185212623008155</v>
+        <v>-4.472611074588953</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.052548535065624</v>
       </c>
       <c r="E73">
-        <v>-6.668112125892089</v>
+        <v>-7.258507396168103</v>
       </c>
       <c r="F73">
-        <v>-1.401611046662716</v>
+        <v>-1.631297446641352</v>
       </c>
       <c r="G73">
-        <v>-5.7717055601999</v>
+        <v>-4.872412417184578</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.031106374737597</v>
       </c>
       <c r="E74">
-        <v>-7.379082545096335</v>
+        <v>-8.009681607612446</v>
       </c>
       <c r="F74">
-        <v>-1.471400171981172</v>
+        <v>-1.397542105980165</v>
       </c>
       <c r="G74">
-        <v>-5.846805285758267</v>
+        <v>-4.649341237657407</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.003199183759917</v>
       </c>
       <c r="E75">
-        <v>-8.193619164856001</v>
+        <v>-7.549638461647223</v>
       </c>
       <c r="F75">
-        <v>-1.385216827393911</v>
+        <v>-1.725939250778598</v>
       </c>
       <c r="G75">
-        <v>-5.724424348808029</v>
+        <v>-4.324444298433333</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.96484295585392</v>
       </c>
       <c r="E76">
-        <v>-8.554203436190761</v>
+        <v>-8.223339539768341</v>
       </c>
       <c r="F76">
-        <v>-1.421406542487416</v>
+        <v>-1.672872378220456</v>
       </c>
       <c r="G76">
-        <v>-5.014931402650203</v>
+        <v>-4.442150745082119</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.909834719392311</v>
       </c>
       <c r="E77">
-        <v>-8.83219739857363</v>
+        <v>-8.335550597204406</v>
       </c>
       <c r="F77">
-        <v>-1.460122778159459</v>
+        <v>-1.800649706837085</v>
       </c>
       <c r="G77">
-        <v>-4.982878700738979</v>
+        <v>-4.064073202315193</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.834463907898987</v>
       </c>
       <c r="E78">
-        <v>-8.947863681677546</v>
+        <v>-9.176361423156576</v>
       </c>
       <c r="F78">
-        <v>-1.890313022883507</v>
+        <v>-1.761511003789614</v>
       </c>
       <c r="G78">
-        <v>-4.962399666033047</v>
+        <v>-4.175151936794359</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.734781343708474</v>
       </c>
       <c r="E79">
-        <v>-8.409047730348895</v>
+        <v>-9.927114486518207</v>
       </c>
       <c r="F79">
-        <v>-1.743254614599316</v>
+        <v>-2.017714272699265</v>
       </c>
       <c r="G79">
-        <v>-4.849324672593701</v>
+        <v>-3.807717797936189</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.610075067613148</v>
       </c>
       <c r="E80">
-        <v>-9.993506443944662</v>
+        <v>-9.837649954022671</v>
       </c>
       <c r="F80">
-        <v>-1.920806883715362</v>
+        <v>-1.76850159630184</v>
       </c>
       <c r="G80">
-        <v>-4.781296272307217</v>
+        <v>-4.112946786111453</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.461717215749368</v>
       </c>
       <c r="E81">
-        <v>-10.45174272878083</v>
+        <v>-10.63311716973604</v>
       </c>
       <c r="F81">
-        <v>-1.912401439679156</v>
+        <v>-2.12130078805194</v>
       </c>
       <c r="G81">
-        <v>-4.595213818090323</v>
+        <v>-3.602361347589658</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.292311837745792</v>
       </c>
       <c r="E82">
-        <v>-11.26517892935663</v>
+        <v>-11.47927159501726</v>
       </c>
       <c r="F82">
-        <v>-2.293808299684938</v>
+        <v>-1.873628875023722</v>
       </c>
       <c r="G82">
-        <v>-4.647431052881247</v>
+        <v>-3.947191081505685</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-4.108589014393641</v>
       </c>
       <c r="E83">
-        <v>-12.78718092943861</v>
+        <v>-12.23497880894328</v>
       </c>
       <c r="F83">
-        <v>-2.401757826148158</v>
+        <v>-2.104539602023695</v>
       </c>
       <c r="G83">
-        <v>-4.386109830193337</v>
+        <v>-4.054902991171412</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.915793023570681</v>
       </c>
       <c r="E84">
-        <v>-13.88141421780802</v>
+        <v>-13.14494396146659</v>
       </c>
       <c r="F84">
-        <v>-2.281347997212027</v>
+        <v>-2.369451497438977</v>
       </c>
       <c r="G84">
-        <v>-4.443527932026456</v>
+        <v>-3.753520856912781</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.724869460738645</v>
       </c>
       <c r="E85">
-        <v>-13.53571504053648</v>
+        <v>-13.35361604374004</v>
       </c>
       <c r="F85">
-        <v>-2.014382579005205</v>
+        <v>-2.223496474535315</v>
       </c>
       <c r="G85">
-        <v>-4.421092364906816</v>
+        <v>-3.589254897799684</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.542479614150047</v>
       </c>
       <c r="E86">
-        <v>-15.40039572572688</v>
+        <v>-16.04584818298816</v>
       </c>
       <c r="F86">
-        <v>-2.418683028922157</v>
+        <v>-2.418651550960851</v>
       </c>
       <c r="G86">
-        <v>-3.781197017621088</v>
+        <v>-3.440277037986941</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.379908418148652</v>
       </c>
       <c r="E87">
-        <v>-16.4151633522097</v>
+        <v>-15.98708670426462</v>
       </c>
       <c r="F87">
-        <v>-2.767099328744046</v>
+        <v>-2.560683425844854</v>
       </c>
       <c r="G87">
-        <v>-4.287144381842364</v>
+        <v>-3.311874218700769</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.243115935916698</v>
       </c>
       <c r="E88">
-        <v>-18.06951453363985</v>
+        <v>-18.14171652321815</v>
       </c>
       <c r="F88">
-        <v>-2.813721502908408</v>
+        <v>-2.470547940378837</v>
       </c>
       <c r="G88">
-        <v>-3.899820485384253</v>
+        <v>-3.562230914562613</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.139323817136911</v>
       </c>
       <c r="E89">
-        <v>-19.31122210654307</v>
+        <v>-19.20874273974949</v>
       </c>
       <c r="F89">
-        <v>-2.745998325892534</v>
+        <v>-2.843145941423249</v>
       </c>
       <c r="G89">
-        <v>-3.453029259404214</v>
+        <v>-2.886667749636778</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.070732210050108</v>
       </c>
       <c r="E90">
-        <v>-19.87980824599814</v>
+        <v>-20.91477739502918</v>
       </c>
       <c r="F90">
-        <v>-3.152967775581307</v>
+        <v>-2.720702470513246</v>
       </c>
       <c r="G90">
-        <v>-4.336756217293882</v>
+        <v>-3.565958588839832</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.041011950269319</v>
       </c>
       <c r="E91">
-        <v>-21.84386176481287</v>
+        <v>-22.84938224737202</v>
       </c>
       <c r="F91">
-        <v>-2.938475290504819</v>
+        <v>-2.854890534460141</v>
       </c>
       <c r="G91">
-        <v>-4.634860911468635</v>
+        <v>-3.541146050022995</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.04938484052231</v>
       </c>
       <c r="E92">
-        <v>-23.25091298068414</v>
+        <v>-24.17650136853391</v>
       </c>
       <c r="F92">
-        <v>-3.166085801772039</v>
+        <v>-2.981373124826194</v>
       </c>
       <c r="G92">
-        <v>-4.486200864027662</v>
+        <v>-4.112519725736887</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.098195049089725</v>
       </c>
       <c r="E93">
-        <v>-25.70648706829141</v>
+        <v>-26.20774838467445</v>
       </c>
       <c r="F93">
-        <v>-3.440446055783652</v>
+        <v>-3.352787388852006</v>
       </c>
       <c r="G93">
-        <v>-4.90197558885027</v>
+        <v>-3.95770206359287</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-3.185182983119912</v>
       </c>
       <c r="E94">
-        <v>-27.94377059483293</v>
+        <v>-27.59931221943949</v>
       </c>
       <c r="F94">
-        <v>-3.452038229218429</v>
+        <v>-3.226251782972173</v>
       </c>
       <c r="G94">
-        <v>-5.675752708289663</v>
+        <v>-4.075772670250977</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-3.311636913011761</v>
       </c>
       <c r="E95">
-        <v>-29.7475614185162</v>
+        <v>-30.40157042741497</v>
       </c>
       <c r="F95">
-        <v>-3.390422605063396</v>
+        <v>-3.380169073351543</v>
       </c>
       <c r="G95">
-        <v>-5.785441013642336</v>
+        <v>-5.383706312451777</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.479500686718416</v>
       </c>
       <c r="E96">
-        <v>-32.41981393044248</v>
+        <v>-32.38923540970568</v>
       </c>
       <c r="F96">
-        <v>-3.586683551971669</v>
+        <v>-3.035299842748442</v>
       </c>
       <c r="G96">
-        <v>-5.988986595578885</v>
+        <v>-4.870624722593371</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.685038367589844</v>
       </c>
       <c r="E97">
-        <v>-34.91304454366053</v>
+        <v>-34.56194063266083</v>
       </c>
       <c r="F97">
-        <v>-3.886297414625028</v>
+        <v>-3.17724722415736</v>
       </c>
       <c r="G97">
-        <v>-5.456875989960749</v>
+        <v>-5.430603500561093</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.938270747121744</v>
       </c>
       <c r="E98">
-        <v>-36.73225934981393</v>
+        <v>-37.37377203468853</v>
       </c>
       <c r="F98">
-        <v>-3.587159863228278</v>
+        <v>-3.300854551268297</v>
       </c>
       <c r="G98">
-        <v>-6.194405946290662</v>
+        <v>-5.648338080678958</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.223162101583142</v>
       </c>
       <c r="E99">
-        <v>-39.72262583959403</v>
+        <v>-39.87635394673242</v>
       </c>
       <c r="F99">
-        <v>-3.839191473897431</v>
+        <v>-3.558134697801587</v>
       </c>
       <c r="G99">
-        <v>-7.200613157496747</v>
+        <v>-6.017477150489853</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.564149016247488</v>
       </c>
       <c r="E100">
-        <v>-42.21790558730055</v>
+        <v>-42.45925287377634</v>
       </c>
       <c r="F100">
-        <v>-3.96670538167997</v>
+        <v>-3.524991718015579</v>
       </c>
       <c r="G100">
-        <v>-7.153219387556541</v>
+        <v>-5.921325665847261</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.918270880638944</v>
       </c>
       <c r="E101">
-        <v>-43.82255223802251</v>
+        <v>-44.09002881952257</v>
       </c>
       <c r="F101">
-        <v>-4.143083854186249</v>
+        <v>-3.570050762890857</v>
       </c>
       <c r="G101">
-        <v>-7.31438336549934</v>
+        <v>-7.310099519571524</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.352585829342031</v>
       </c>
       <c r="E102">
-        <v>-46.84891556768958</v>
+        <v>-47.16667632457081</v>
       </c>
       <c r="F102">
-        <v>-3.95486055618734</v>
+        <v>-3.799164760994159</v>
       </c>
       <c r="G102">
-        <v>-7.641077930951239</v>
+        <v>-7.000924361113448</v>
       </c>
     </row>
   </sheetData>
